--- a/Team-Data/2012-13/1-13-2012-13.xlsx
+++ b/Team-Data/2012-13/1-13-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,19 +806,19 @@
         <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH2" t="n">
         <v>11</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
@@ -763,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -954,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
@@ -978,7 +1045,7 @@
         <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
         <v>27</v>
@@ -993,7 +1060,7 @@
         <v>17</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>16</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1025,73 +1092,73 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.595</v>
+        <v>0.583</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L4" t="n">
         <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P4" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S4" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
         <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X4" t="n">
         <v>4.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA4" t="n">
         <v>21.4</v>
@@ -1100,25 +1167,25 @@
         <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1130,10 +1197,10 @@
         <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
@@ -1142,10 +1209,10 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1154,10 +1221,10 @@
         <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
@@ -1175,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
@@ -1315,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>3</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1330,13 +1397,13 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>18</v>
       </c>
       <c r="AU5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV5" t="n">
         <v>6</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1467,13 +1534,13 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
@@ -1515,13 +1582,13 @@
         <v>15</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1530,7 +1597,7 @@
         <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
         <v>13</v>
@@ -1542,7 +1609,7 @@
         <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="n">
         <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>0.231</v>
+        <v>0.237</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.418</v>
+        <v>0.419</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P7" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S7" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T7" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U7" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="V7" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W7" t="n">
         <v>8.300000000000001</v>
@@ -1634,22 +1701,22 @@
         <v>3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Z7" t="n">
         <v>22.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.7</v>
+        <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1661,13 +1728,13 @@
         <v>29</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1676,31 +1743,31 @@
         <v>10</v>
       </c>
       <c r="AM7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU7" t="n">
         <v>30</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>29</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
@@ -1718,7 +1785,7 @@
         <v>29</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
         <v>21</v>
@@ -1846,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
         <v>5</v>
@@ -1864,10 +1931,10 @@
         <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ8" t="n">
         <v>6</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
         <v>17</v>
@@ -1891,7 +1958,7 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -1900,7 +1967,7 @@
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -1935,97 +2002,97 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.59</v>
+        <v>0.579</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K9" t="n">
         <v>0.464</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="N9" t="n">
         <v>0.329</v>
       </c>
       <c r="O9" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P9" t="n">
         <v>25.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.68</v>
+        <v>0.678</v>
       </c>
       <c r="R9" t="n">
         <v>14.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
         <v>46.4</v>
       </c>
       <c r="U9" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.4</v>
+        <v>102</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2067,19 +2134,19 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2225,10 +2292,10 @@
         <v>26</v>
       </c>
       <c r="AN10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2246,10 +2313,10 @@
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
@@ -2264,7 +2331,7 @@
         <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -2299,94 +2366,94 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
         <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>0.639</v>
+        <v>0.657</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
         <v>83.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.392</v>
+        <v>0.387</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="R11" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="S11" t="n">
         <v>34.1</v>
       </c>
       <c r="T11" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X11" t="n">
         <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>10</v>
@@ -2407,28 +2474,28 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
         <v>27</v>
@@ -2446,13 +2513,13 @@
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2595,7 +2662,7 @@
         <v>4</v>
       </c>
       <c r="AP12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>15</v>
@@ -2622,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>8</v>
@@ -2631,10 +2698,10 @@
         <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2730,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.605</v>
+        <v>0.622</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
         <v>81</v>
@@ -2690,61 +2757,61 @@
         <v>6.5</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P13" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="S13" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T13" t="n">
-        <v>46.1</v>
+        <v>46.3</v>
       </c>
       <c r="U13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X13" t="n">
         <v>6.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z13" t="n">
         <v>19.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
         <v>6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2771,22 +2838,22 @@
         <v>17</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>2</v>
@@ -2795,28 +2862,28 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -2977,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.432</v>
+        <v>0.417</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
       <c r="L15" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>25.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
         <v>19.9</v>
@@ -3066,76 +3133,76 @@
         <v>28.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="S15" t="n">
         <v>32.7</v>
       </c>
       <c r="T15" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U15" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
         <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>103.4</v>
+        <v>103.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK15" t="n">
         <v>11</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3156,22 +3223,22 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3320,10 +3387,10 @@
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3347,16 +3414,16 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3499,7 +3566,7 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,10 +3593,10 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3573,106 +3640,106 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
         <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J18" t="n">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.432</v>
       </c>
       <c r="L18" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>17.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O18" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="R18" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="X18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG18" t="n">
         <v>16</v>
-      </c>
-      <c r="P18" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="T18" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="V18" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,34 +3748,34 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
         <v>1</v>
@@ -3717,16 +3784,16 @@
         <v>4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3755,91 +3822,91 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
         <v>16</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" t="n">
-        <v>0.471</v>
+        <v>0.485</v>
       </c>
       <c r="H19" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.429</v>
+        <v>0.431</v>
       </c>
       <c r="L19" t="n">
         <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.297</v>
+        <v>0.298</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S19" t="n">
-        <v>31.6</v>
+        <v>31.9</v>
       </c>
       <c r="T19" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V19" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3848,10 +3915,10 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3869,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
@@ -3881,22 +3948,22 @@
         <v>11</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
       </c>
       <c r="AY19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>3</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -3937,43 +4004,43 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" t="n">
-        <v>0.297</v>
+        <v>0.306</v>
       </c>
       <c r="H20" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I20" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J20" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L20" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="O20" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="Q20" t="n">
         <v>0.777</v>
@@ -3982,16 +4049,16 @@
         <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W20" t="n">
         <v>6.4</v>
@@ -4000,22 +4067,22 @@
         <v>5.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>91.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4027,7 +4094,7 @@
         <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI20" t="n">
         <v>23</v>
@@ -4045,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="n">
         <v>27</v>
@@ -4057,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="AR20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>20</v>
@@ -4069,22 +4136,22 @@
         <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
         <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
         <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>0.649</v>
+        <v>0.639</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4149,70 +4216,70 @@
         <v>28.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O21" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P21" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R21" t="n">
         <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
         <v>11.1</v>
       </c>
       <c r="W21" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
         <v>3.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB21" t="n">
         <v>101.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ21" t="n">
         <v>6</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4245,7 +4312,7 @@
         <v>26</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
@@ -4263,7 +4330,7 @@
         <v>3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -4301,52 +4368,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.784</v>
+        <v>0.778</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J22" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L22" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.392</v>
+        <v>0.396</v>
       </c>
       <c r="O22" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.839</v>
+        <v>0.84</v>
       </c>
       <c r="R22" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T22" t="n">
         <v>43.4</v>
@@ -4361,25 +4428,25 @@
         <v>8.1</v>
       </c>
       <c r="X22" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.2</v>
+        <v>105.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,10 +4458,10 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4403,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,16 +4494,16 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,13 +4512,13 @@
         <v>2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE23" t="n">
         <v>24</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
@@ -4752,7 +4819,7 @@
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4794,7 +4861,7 @@
         <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-4.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>24</v>
       </c>
       <c r="AF25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
         <v>26</v>
@@ -4940,16 +5007,16 @@
         <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK25" t="n">
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM25" t="n">
         <v>23</v>
@@ -4964,7 +5031,7 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
         <v>16</v>
@@ -4973,7 +5040,7 @@
         <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
         <v>13</v>
@@ -4982,19 +5049,19 @@
         <v>5</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>8</v>
       </c>
       <c r="AY25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0.541</v>
+        <v>0.556</v>
       </c>
       <c r="H26" t="n">
         <v>48.8</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J26" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M26" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O26" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R26" t="n">
         <v>12</v>
@@ -5080,13 +5147,13 @@
         <v>41.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V26" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W26" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
@@ -5095,31 +5162,31 @@
         <v>4.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
         <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>13</v>
       </c>
       <c r="AF26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG26" t="n">
         <v>13</v>
       </c>
-      <c r="AG26" t="n">
-        <v>14</v>
-      </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="n">
         <v>20</v>
@@ -5128,7 +5195,7 @@
         <v>12</v>
       </c>
       <c r="AK26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
         <v>20</v>
@@ -5146,7 +5213,7 @@
         <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
         <v>13</v>
@@ -5155,16 +5222,16 @@
         <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AX26" t="n">
         <v>21</v>
@@ -5179,7 +5246,7 @@
         <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
         <v>21</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>17</v>
@@ -5322,7 +5389,7 @@
         <v>15</v>
       </c>
       <c r="AO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
@@ -5334,7 +5401,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT27" t="n">
         <v>25</v>
@@ -5346,13 +5413,13 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ27" t="n">
         <v>25</v>
@@ -5361,7 +5428,7 @@
         <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.725</v>
+        <v>0.718</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="J28" t="n">
         <v>81.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.485</v>
+        <v>0.483</v>
       </c>
       <c r="L28" t="n">
         <v>8.800000000000001</v>
@@ -5426,49 +5493,49 @@
         <v>0.389</v>
       </c>
       <c r="O28" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.795</v>
       </c>
       <c r="R28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="S28" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T28" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
         <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AB28" t="n">
         <v>104.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5495,19 +5562,19 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
         <v>3</v>
@@ -5516,10 +5583,10 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5531,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="AX28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
         <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5593,103 +5660,103 @@
         <v>35.8</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.437</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0.775</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S29" t="n">
-        <v>29.2</v>
+        <v>29.4</v>
       </c>
       <c r="T29" t="n">
         <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V29" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
         <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB29" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
         <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -5698,7 +5765,7 @@
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5710,10 +5777,10 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5853,7 +5920,7 @@
         <v>18</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK30" t="n">
         <v>13</v>
@@ -5865,7 +5932,7 @@
         <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6123,7 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
         <v>15</v>
@@ -6071,16 +6138,16 @@
         <v>23</v>
       </c>
       <c r="AV31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>23</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
         <v>22</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-13-2012-13</t>
+          <t>2013-01-13</t>
         </is>
       </c>
     </row>
